--- a/Result/pareto_front_sensitivity.xlsx
+++ b/Result/pareto_front_sensitivity.xlsx
@@ -495,7 +495,7 @@
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>888.0896</v>
+        <v>1006.8176</v>
       </c>
       <c r="H2" t="n">
         <v>1.9139</v>
@@ -524,7 +524,7 @@
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>817.8625</v>
+        <v>941.8753</v>
       </c>
       <c r="H3" t="n">
         <v>1.7787</v>
@@ -553,7 +553,7 @@
         <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>722.0327</v>
+        <v>847.4947</v>
       </c>
       <c r="H4" t="n">
         <v>1.6352</v>
@@ -582,10 +582,10 @@
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>589.9656</v>
+        <v>707.4215</v>
       </c>
       <c r="H5" t="n">
-        <v>1.4687</v>
+        <v>1.4887</v>
       </c>
       <c r="I5" t="n">
         <v>2.5681</v>
@@ -611,10 +611,10 @@
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>485.2141</v>
+        <v>587.5444</v>
       </c>
       <c r="H6" t="n">
-        <v>1.2052</v>
+        <v>1.2712</v>
       </c>
       <c r="I6" t="n">
         <v>2.462</v>
@@ -640,10 +640,10 @@
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>393.6594</v>
+        <v>475.0077</v>
       </c>
       <c r="H7" t="n">
-        <v>1.0208</v>
+        <v>1.0868</v>
       </c>
       <c r="I7" t="n">
         <v>2.3825</v>
@@ -669,10 +669,10 @@
         <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>427.0394</v>
+        <v>543.1409</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9827</v>
+        <v>1.0487</v>
       </c>
       <c r="I8" t="n">
         <v>2.2395</v>
@@ -698,10 +698,10 @@
         <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>301.3643</v>
+        <v>371.1885</v>
       </c>
       <c r="H9" t="n">
-        <v>0.7983</v>
+        <v>0.8643</v>
       </c>
       <c r="I9" t="n">
         <v>2.16</v>
@@ -727,10 +727,10 @@
         <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>357.6029</v>
+        <v>498.9721</v>
       </c>
       <c r="H10" t="n">
-        <v>0.7847</v>
+        <v>0.8507</v>
       </c>
       <c r="I10" t="n">
         <v>2.0415</v>
@@ -756,10 +756,10 @@
         <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>164.735</v>
+        <v>159.9786</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6002999999999999</v>
+        <v>0.6663</v>
       </c>
       <c r="I11" t="n">
         <v>1.962</v>
@@ -785,10 +785,10 @@
         <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>169.4958</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0.5417</v>
+        <v>0.6077</v>
       </c>
       <c r="I12" t="n">
         <v>1.9034</v>
@@ -815,7 +815,7 @@
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>0.4797</v>
+        <v>0.5456</v>
       </c>
       <c r="I13" t="n">
         <v>1.8414</v>

--- a/Result/pareto_front_sensitivity.xlsx
+++ b/Result/pareto_front_sensitivity.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -489,13 +489,13 @@
         <v>3.0851</v>
       </c>
       <c r="E2" t="n">
-        <v>6.0342</v>
+        <v>21.8625</v>
       </c>
       <c r="F2" t="b">
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>1006.8176</v>
+        <v>1177.4658</v>
       </c>
       <c r="H2" t="n">
         <v>1.9139</v>
@@ -506,263 +506,263 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="n">
         <v>0.75</v>
       </c>
-      <c r="C3" t="n">
-        <v>1</v>
-      </c>
       <c r="D3" t="n">
-        <v>2.657</v>
+        <v>2.8625</v>
       </c>
       <c r="E3" t="n">
-        <v>15.5633</v>
+        <v>31.2588</v>
       </c>
       <c r="F3" t="b">
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>941.8753</v>
+        <v>1269.3505</v>
       </c>
       <c r="H3" t="n">
-        <v>1.7787</v>
+        <v>1.6914</v>
       </c>
       <c r="I3" t="n">
-        <v>3.5354</v>
+        <v>4.0337</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="B4" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="C4" t="n">
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.2207</v>
+        <v>2.657</v>
       </c>
       <c r="E4" t="n">
-        <v>25.0923</v>
+        <v>31.3871</v>
       </c>
       <c r="F4" t="b">
         <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>847.4947</v>
+        <v>1124.8372</v>
       </c>
       <c r="H4" t="n">
-        <v>1.6352</v>
+        <v>1.7787</v>
       </c>
       <c r="I4" t="n">
-        <v>2.8063</v>
+        <v>3.5354</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2.5</v>
+        <v>7.5</v>
       </c>
       <c r="B5" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7815</v>
+        <v>2.4345</v>
       </c>
       <c r="E5" t="n">
-        <v>34.6214</v>
+        <v>40.7834</v>
       </c>
       <c r="F5" t="b">
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>707.4215</v>
+        <v>1227.7896</v>
       </c>
       <c r="H5" t="n">
-        <v>1.4887</v>
+        <v>1.5562</v>
       </c>
       <c r="I5" t="n">
-        <v>2.5681</v>
+        <v>3.3129</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="C6" t="n">
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5181</v>
+        <v>2.2207</v>
       </c>
       <c r="E6" t="n">
-        <v>40.3389</v>
+        <v>40.9118</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>587.5444</v>
+        <v>1035.3268</v>
       </c>
       <c r="H6" t="n">
-        <v>1.2712</v>
+        <v>1.6352</v>
       </c>
       <c r="I6" t="n">
-        <v>2.462</v>
+        <v>2.8063</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3337</v>
+        <v>1.9982</v>
       </c>
       <c r="E7" t="n">
-        <v>44.1505</v>
+        <v>50.3081</v>
       </c>
       <c r="F7" t="b">
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>475.0077</v>
+        <v>1143.8894</v>
       </c>
       <c r="H7" t="n">
-        <v>1.0868</v>
+        <v>1.4126</v>
       </c>
       <c r="I7" t="n">
-        <v>2.3825</v>
+        <v>2.5838</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="B8" t="n">
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
       <c r="C8" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.2956</v>
+        <v>1.7815</v>
       </c>
       <c r="E8" t="n">
-        <v>50.363</v>
+        <v>50.4364</v>
       </c>
       <c r="F8" t="b">
         <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>543.1409</v>
+        <v>873.1624</v>
       </c>
       <c r="H8" t="n">
-        <v>1.0487</v>
+        <v>1.4887</v>
       </c>
       <c r="I8" t="n">
-        <v>2.2395</v>
+        <v>2.5681</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="C9" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.1111</v>
+        <v>1.5181</v>
       </c>
       <c r="E9" t="n">
-        <v>54.1746</v>
+        <v>56.1512</v>
       </c>
       <c r="F9" t="b">
         <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>371.1885</v>
+        <v>698.0967000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8643</v>
+        <v>1.2712</v>
       </c>
       <c r="I9" t="n">
-        <v>2.16</v>
+        <v>2.462</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B10" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1.0976</v>
+        <v>1.3337</v>
       </c>
       <c r="E10" t="n">
-        <v>60.6256</v>
+        <v>59.9611</v>
       </c>
       <c r="F10" t="b">
         <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>498.9721</v>
+        <v>490.083</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8507</v>
+        <v>1.0868</v>
       </c>
       <c r="I10" t="n">
-        <v>2.0415</v>
+        <v>2.3825</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="C11" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9132</v>
+        <v>1.2956</v>
       </c>
       <c r="E11" t="n">
-        <v>64.4372</v>
+        <v>65.5475</v>
       </c>
       <c r="F11" t="b">
         <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>159.9786</v>
+        <v>649.4063</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6663</v>
+        <v>1.0487</v>
       </c>
       <c r="I11" t="n">
-        <v>1.962</v>
+        <v>2.2395</v>
       </c>
     </row>
     <row r="12">
@@ -773,51 +773,134 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8546</v>
+        <v>1.1111</v>
       </c>
       <c r="E12" t="n">
-        <v>76.0094</v>
+        <v>69.3574</v>
       </c>
       <c r="F12" t="b">
         <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>73.66759999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>0.6077</v>
+        <v>0.8643</v>
       </c>
       <c r="I12" t="n">
-        <v>1.9034</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D13" t="n">
+        <v>1.0976</v>
+      </c>
+      <c r="E13" t="n">
+        <v>75.1771</v>
+      </c>
+      <c r="F13" t="b">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.8507</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.0415</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>0</v>
+      </c>
+      <c r="B14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.9132</v>
+      </c>
+      <c r="E14" t="n">
+        <v>78.98699999999999</v>
+      </c>
+      <c r="F14" t="b">
+        <v>1</v>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="n">
+        <v>0.6663</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.962</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>0</v>
+      </c>
+      <c r="B15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.8546</v>
+      </c>
+      <c r="E15" t="n">
+        <v>89.9263</v>
+      </c>
+      <c r="F15" t="b">
+        <v>1</v>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="n">
+        <v>0.6077</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.9034</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>0</v>
+      </c>
+      <c r="B16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
         <v>0.7925</v>
       </c>
-      <c r="E13" t="n">
-        <v>87.57089999999999</v>
-      </c>
-      <c r="F13" t="b">
-        <v>1</v>
-      </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="n">
+      <c r="E16" t="n">
+        <v>100.834</v>
+      </c>
+      <c r="F16" t="b">
+        <v>1</v>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="n">
         <v>0.5456</v>
       </c>
-      <c r="I13" t="n">
+      <c r="I16" t="n">
         <v>1.8414</v>
       </c>
     </row>

--- a/Result/pareto_front_sensitivity.xlsx
+++ b/Result/pareto_front_sensitivity.xlsx
@@ -495,7 +495,7 @@
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>1177.4658</v>
+        <v>1249.8257</v>
       </c>
       <c r="H2" t="n">
         <v>1.9139</v>
@@ -524,7 +524,7 @@
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>1269.3505</v>
+        <v>1357.2945</v>
       </c>
       <c r="H3" t="n">
         <v>1.6914</v>
@@ -553,7 +553,7 @@
         <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>1124.8372</v>
+        <v>1212.9005</v>
       </c>
       <c r="H4" t="n">
         <v>1.7787</v>
@@ -582,7 +582,7 @@
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>1227.7896</v>
+        <v>1340.0669</v>
       </c>
       <c r="H5" t="n">
         <v>1.5562</v>
@@ -611,7 +611,7 @@
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>1035.3268</v>
+        <v>1147.7892</v>
       </c>
       <c r="H6" t="n">
         <v>1.6352</v>
@@ -640,7 +640,7 @@
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>1143.8894</v>
+        <v>1299.0989</v>
       </c>
       <c r="H7" t="n">
         <v>1.4126</v>
@@ -669,7 +669,7 @@
         <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>873.1624</v>
+        <v>1028.7184</v>
       </c>
       <c r="H8" t="n">
         <v>1.4887</v>
@@ -698,7 +698,7 @@
         <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>698.0967000000001</v>
+        <v>900.093</v>
       </c>
       <c r="H9" t="n">
         <v>1.2712</v>
@@ -727,7 +727,7 @@
         <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>490.083</v>
+        <v>742.2204</v>
       </c>
       <c r="H10" t="n">
         <v>1.0868</v>
@@ -756,7 +756,7 @@
         <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>649.4063</v>
+        <v>1049.1549</v>
       </c>
       <c r="H11" t="n">
         <v>1.0487</v>
@@ -785,7 +785,7 @@
         <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>73.66759999999999</v>
+        <v>732.8276</v>
       </c>
       <c r="H12" t="n">
         <v>0.8643</v>
@@ -813,9 +813,7 @@
       <c r="F13" t="b">
         <v>1</v>
       </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
         <v>0.8507</v>
       </c>
